--- a/output/4o-mini-filtered.xlsx
+++ b/output/4o-mini-filtered.xlsx
@@ -508,7 +508,7 @@
         <v>183</v>
       </c>
       <c r="C3" t="n">
-        <v>83.06010928961749</v>
+        <v>82.5136612021858</v>
       </c>
       <c r="D3" t="n">
         <v>132</v>
@@ -520,10 +520,10 @@
         <v>51</v>
       </c>
       <c r="G3" t="n">
-        <v>43.13725490196079</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="H3" t="n">
-        <v>10.92896174863388</v>
+        <v>10.3825136612022</v>
       </c>
     </row>
     <row r="4">
